--- a/barcode_prefix_tabs.xlsx
+++ b/barcode_prefix_tabs.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>G0001745991; G0001746007; G0001746015; G0001746023; G0001746031; G0001746049; G0001746056; G0001746064; G0001746072; G0001746080; G0001746098; G0001746106; G0001746114; G0001746122; G0001746130; G0001746148; G0001746155; G0001746163; G0001746171; G0001746189; G0001746197; G0001746205; G0001746213; G0001746221; G0001746239; G0001746247; G0001746254; G0001746262; G0001746270; G0001746288; G0001746296; G0001746304; G0001746312; G0001746320; G0001746338; G0001746346; G0001746353; G0001746361; G0001746379; G0001746387; G0001746395; G0001746403; G0001746411; G0001746429; G0001746437; G0001746445; G0001746452; G0001746460; G0001746478; G0001746486; G0001746494; G0001746502; G0001746510; G0001746528; G0001746536; G0001746544; G0001746551; G0001746569; G0001746577; G0001746585; G0001746593; G0001746601; G0001746619; G0001746627; G0001746635; G0001746643; G0001746650; G0001746668; G0001746676; G0001746684; G0001746692; G0001746700; G0001746718; G0001746726; G0001746734; G0001746742; G0001746759; G0001746767; G0001746775; G0001746783; G0001746791; G0001746809; G0001746817; G0001746825; G0001746833; G0001746841; G0001746858; G0001746866; G0001746874; G0001746882; G0001746890; G0001746908; G0001746916; G0001746924; G0001746932; G0001746940; G0001746957; G0001746965; G0001746973; G0001746981; G0001746999; G0001747005; G0001747013; G0001747021; G0001747039; G0001747047; G0001747054; G0001747062; G0001747070; G0001747088; G0001747096; G0001747104; G0001747112; G0001747120; G0001747138; G0001747146; G0001747153; G0001747161; G0001747179; G0001747187; G0001747195; G0001747203; G0001747211; G0001747229; G0001747237; G0001747245; G0001747252; G0001747260; G0001747278; G0001747286; G0001747294; G0001747302; G0001747310; G0001747328; G0001747336; G0001747344; G0001747351; G0001747369; G0001747377; G0001747385; G0001747393; G0001747401; G0001747419; G0001747427; G0001747435; G0001747443; G0001747450; G0001747468; G0001747476; G0001747484; G0001747492; G0001747500; G0001747518; G0001747526; G0001747534; G0001747542; G0001747559; G0001747567; G0001747575; G0001747583; G0001747591; G0001747609; G0001747617; G0001747625; G0001747633; G0001747641; G0001747658; G0001747666; G0001747674; G0001747682; G0001747690; G0001747708; G0001747716; G0001747724; G0001747732; G0001747740; G0001747757; G0001747765; G0001747773; G0001747781; G0001747799; G0001747807; G0001747815; G0001747823; G0001747831; G0001747849; G0001747856; G0001747864; G0001747872; G0001747880; G0001747898; G0001747906; G0001747914; G0001747922; G0001747930; G0001747948; G0001747955; G0001747963; G0001747971; G0001747989; G0001747997; G0001748003; G0001748011; G0001748029; G0001748037; G0001748045; G0001748052; G0001748060; G0001748078; G0001748086; G0001748094; G0001748102; G0001748110; G0001748128; G0001748136; G0001748144; G0001748151; G0001748169; G0001748177; G0001748185; G0001748193; G0001748201; G0001748219; G0001748227; G0001748235; G0001748243; G0001748250; G0001748268; G0001748276; G0001748284; G0001748292; G0001748300; G0001748318; G0001748326; G0001748334; G0001748342; G0001748359; G0001748367; G0001748375; G0001748391; G0001748409; G0001748417; G0001748425; G0001748433; G0001748441; G0001748458; G0001748466; G0001748474; G0001748482; G0001748490; G0001748508; G0001748516; G0001748524; G0001748532; G0001748540; G0001748557; G0001748565; G0001748573; G0001748581; G0001748599; G0001748607; G0001748615; G0001748623; G0001748631; G0001748649; G0001748656; G0001748664; G0001748672; G0001748680; G0001748698; G0001748706; G0001748714; G0001748722; G0001748730; G0001748748; G0001748755; G0001748763; G0001748771; G0001748789; G0001748797; G0001748805; G0001748813; G0001748821; G0001748839; G0001748847; G0001748854; G0001748862; G0001748870; G0001748888; G0001748896; G0001748904; G0001748912; G0001748920; G0001748938; G0001748946; G0001748953; G0001748961; G0001748979; G0001748987; G0001748995; G0001749001; G0001749019; G0001749027; G0001749035; G0001749043; G0001749050; G0001749068; G0001749076; G0001749084; G0001749092; G0001749100; G0001749118; G0001749126; G0001749134; G0001749142; G0001749159; G0001749167; G0001749175; G0001749183; G0001749191; G0001749209; G0001749217; G0001749225; G0001749233; G0001749241; G0001749258; G0001749266; G0001749274; G0001749282; G0001749290; G0001749308; G0001749316; G0001749324; G0001749332; G0001749340; G0001749357; G0001749365; G0001749373; G0001749381; G0001749399; G0001749407; G0001749415; G0001749423; G0001749431; G0001749449; G0001749456; G0001749464; G0001749472; G0001749480; G0001749498; G0001749506; G0001749514; G0001749522; G0001749530; G0001749548; G0001749555; G0001749563; G0001749571; G0001749589; G0001749597; G0001749605; G0001749613; G0001749621; G0001749639; G0001749647; G0001749654; G0001749662; G0001749670; G0001749688; G0001749696; G0001749704; G0001749712; G0001749720; G0001749738; G0001749746; G0001749753; G0001749761; G0001749779; G0001749787; G0001749795; G0001749803; G0001749811; G0001749829; G0001749837; G0001749845; G0001749852; G0001749860; G0001749878; G0001749886; G0001749894; G0001749902; G0001749910; G0001749928; G0001749936; G0001749944; G0001749951; G0001749969; G0001749977; G0001749985; G0001749993; G0001750009; G0001750017; G0001750025; G0001750033; G0001750041; G0001750058; G0001750066; G0001750074; G0001750082; G0001750090; G0001750108; G0001750116; G0001750124; G0001750132; G0001750140; G0001750157; G0001750165; G0001750173; G0001750181; G0001750199; G0001750207; G0001750215; G0001750223; G0001750231; G0001750249; G0001750256; G0001750264; G0001750272; G0001750280; G0001750298; G0001750306; G0001750314; G0001750322; G0001750330; G0001750348; G0001750355; G0001750363; G0001750371; G0001750389; G0001750397; G0001750405; G0001750413; G0001750421; G0001750439; G0001750447; G0001750454; G0001750462; G0001750470; G0001750488; G0001750496; G00017505043; G0001750512; G0001750538; G0001750546; G0001750553; G0001750561; G0001750579; G0001750587; G0001750595; G0001750603; G0001750611; G0001750629; G0001750637; G0001750645; G0001750652; G0001750660; G0001750678; G0001750686; G0001750694; G0001750702; G0001750710; G0001750728; G0001750736; G0001750744; G0001750751; G0001750769; G0001750777; G0001750785; G0001750793; G0001750801; G0001750819; G0001750827; G0001750835; G0001750843; G0001750850; G0001750868; G0001750876; G0001750884; G0001750892; G0001750900; G0001750918; G0001750926; G0001750934; G0001750942; G0001750959; G0001750967; G0001750975; G0001750983; G0001750991; G0001751007; G0001751015; G0001751023; G0001751031; G0001751049; G0001751056; G0001751064; G0001751072; G0001751080; G0001751098; G0001751106; G0001751114; G0001751122; G0001751130; G0001751148; G0001751155; G0001751163; G0001751171; G0001751189; G0001751197; G0001751205; G0001751213; G0001751221; G0001751239; G0001751247; G0001751254; G0001751262; G0001751270; G0001751288; G0001751296; G0001751304; G0001751312; G0001751320; G0001751338; G0001751346; G0001751353; G0001751361; G0001751379; G0001751387; G0001751395; G0001751403; G0001751411; G0001751429; G0001751437; G0001751445; G0001751452; G0001751460; G0001751478; G0001751486; G0001751494; G0001751502; G0001751510; G0001751528; G0001751536; G0001751544; G0001751551; G0001751569; G0001751577; G0001751585; G0001751593; G0001751601; G0001751619; G0001751627; G0001751635; G0001751643; G0001751650; G0001751668; G0001751676; G0001751684; G0001751692; G0001751700; G0001751718; G0001751726; G0001751734; G0001751742; G0001751759; G0001751767; G0001751775; G0001751783; G0001751791; G0001751809; G0001751817; G0001751825; G0001751833; G0001751841; G0001751858; G0001751866; G0001751874; G0001751882; G0001751890; G0001751908; G0001751916; G0001751924; G0001751932; G0001751940; G0001751957; G0001751965; G0001751973; G0001751981; G0001751999; G0001752005; G0001752013; G0001752021; G0001752039; G0001752047; G0001752054; G0001752062; G0001752070; G0001752088; G0001752096; G0001752104; G0001752112; G0001752120; G0001752138; G0001752146; G0001752153; G0001752161; G0001752179; G0001752187; G0001752195; G0001752203; G0001752211; G0001752229; G0001752237; G0001752245; G0001752252; G0001752260; G0001752278; G0001752286; G0001752294; G0001752302; G0001752310; G0001752328; G0001752336; G0001752344; G0001752351; G0001752369; G0001752377; G0001752385; G0001752393; G0001752401; G0001752419; G0001752427; G0001752435; G0001752443; G0001752450; G0001752468; G0001752476; G0001752484; G0001752492; G0001752500; G0001752518; G0001752526; G0001752534; G0001752542; G0001752559; G0001752567; G0001752575; G0001752583; G0001752591; G0001752609; G0001752617; G0001752625; G0001752633; G0001752641; G0001752658; G0001752666; G0001752674; G0001752682; G0001752690; G0001752708; G0001752716; G0001752724; G0001752732; G0001752740; G0001752757; G0001752765; G0001752773; G0001752781; G0001752799; G0001752807; G0001752815; G0001752823; G0001752831; G0001752849; G0001752856; G0001752864; G0001752872; G0001752880; G0001752898; G0001752906; G0001752914; G0001752922; G0001752930; G0001752948; G0001752955; G0001752963; G0001752964; G0001752971; G0001752989; G0001752997; G0001753003; G0001753011; G0001753029; G0001753037; G0001753045; G0001753052; G0001753060; G0001753078; G0001753086; G0001753094; G0001753102; G0001753110; G0001753128; G0001753136; G0001753144; G0001753151; G0001753169; G0001753177; G0001753185; G0001753193; G0001753201; G0001753219; G0001753227; G0001753235; G0001753243; G0001753250; G0001753268; G0001753276; G0001753284; G0001753292; G0001753300; G0001753318; G0001753326; G0001753334; G0001753342; G0001753359; G0001753367; G0001753375; G0001753383; G0001753391; G0001753409; G0001753417; G0001753425; G0001753433; G0001753441; G0001753458; G0001753466; G0001753474; G0001753482; G0001753490; G0001753508; G0001753516; G0001753524; G0001753532; G0001753540; G0001753557; G0001753565; G0001753573; G0001753581; G0001753599; G0001753607; G0001753615; G0001753623; G0001753631; G0001753649; G0001753656; G0001753664; G0001753672; G0001753680; G0001753698; G0001753706; G0001753714; G0001753722; G0001753730; G0001753748; G0001753755; G0001753763; G0001753771; G0001753789; G0001753797; G0001753805; G0001753813; G0001753821; G0001753839; G0001753847; G0001753854; G0001753862; G0001753870; G0001753888; G0001753896; G0001753904; G0001753912; G0001753920; G0001753938; G0001753946; G0001753953; G0001753961; G0001753979; G0001753987; G0001753995; G0001754001; G0001754019; G0001754027; G0001754035; G0001754043; G0001754050; G0001754068; G0001754076; G0001754084; G0001754092; G0001754100; G0001754118; G0001754126; G0001754142; G0001754159; G0001754167; G0001754175; G0001754183; G0001754191; G0001754209; G0001754217; G0001754225; G0001754233; G0001754241; G0001754258; G0001754266; G0001754274; G0001754282; G0001754290; G0001754308; G0001754316; G0001754324; G0001754332; G0001754340; G0001754357; G0001754365; G0001754373; G0001754381; G0001754399; G0001754407; G0001754415; G0001754423; G0001754431; G0001754449; G0001754456; G0001754464; G0001754472; G0001754480; G0001754498; G0001754506; G0001754514; G0001754522; G0001754530; G0001754548; G0001754555; G0001754563; G0001754571; G0001754589; G0001754597; G0001754605; G0001754613; G0001754621; G0001754639; G0001754647; G0001754654; G0001754662; G0001754670; G0001754688; G0001754696; G0001754704; G0001754712; G0001754720; G0001754738; G0001754746; G0001754753; G0001754761; G0001754779; G0001754787; G0001754795; G000175480W; G0001754811; G0001754829; G0001754837; G0001754845; G0001754852; G0001754860; G0001754878; G0001754886; G0001754894; G0001754902; G0001754910; G0001754928; G0001754936; G0001754944; G0001754951; G0001754969; G0001754977; G0001754985; G0001754993; G0001755008; G0001755016; G0001755024; G0001755032; G0001755040; G0001755057; G0001755065; G0001755073; G0001755081; G0001755099; G0001755107; G0001755115; G0001755123; G0001755131; G0001755149; G0001755156; G0001755164; G0001755172; G0001755180; G0001755198; G0001755206; G0001755214; G0001755222; G0001755230; G0001755248; G0001755255; G0001755263; G0001755271; G0001755289; G0001755297; G0001755305; G0001755313; G0001755321; G0001755339; G0001755347; G0001755354; G0001755362; G0001755370; G0001755388; G0001755396; G0001755404; G0001755412; G0001755420; G0001755438; G0001755446; G0001755453; G0001755461; G0001755479; G0001755487; G0001755495; G0001755503; G0001755511; G0001755529; G0001755537; G0001755545; G0001755552; G0001755560; G0001755578; G0001755586; G0001755594; G0001755602; G0001755610; G0001755628; G0001755636; G0001755644; G0001755651; G0001755669; G0001755677; G0001755685; G0001755693; G0001755701; G0001755719; G0001755727; G0001755735; G0001755743; G0001755750; G0001755768; G0001755776; G0001755784; G0001755792; G0001755800; G0001755818; G0001755826; G0001755834; G0001755842; G0001755859; G0001755867; G0001755875; G0001755883; G0001755891; G0001755900; G0001755909; G0001755917; G0001755925; G0001755933; G0001755941; G0001755958; G0001755966; G0001755974; G0001755982; G0001756006; G0001756014; G0001756022; G0001756030; G0001756048; G0001756055; G0001756063; G0001756071; G0001756089; G0001756097; G0001756105; G0001756113; G0001756121; G0001756139; G0001756147; G0001756154; G0001756162; G0001756170; G0001756188; G0001756196; G0001756204; G0001756212; G0001756220; G0001756238; G0001756246; G0001756253; G0001756261; G0001756279; G0001756287; G0001756295; G0001756303; G0001756311; G0001756329; G0001756337; G0001756345; G0001756352; G0001756360; G0001756378; G0001756386; G0001756394; G0001756402; G0001756410; G0001756428; G0001756436; G0001756444; G0001756451; G0001756469; G0001756477; G0001756485; G0001756493; G0001756501; G0001756519; G0001756527; G0001756535; G0001756543; G0001756550; G0001756568; G0001756576; G0001756584; G0001756592; G0001756600; G0001756618; G0001756626; G0001756634; G0001756642; G0001756659; G0001756667; G0001756675; G0001756683; G0001756691; G0001756709; G0001756717; G0001756725; G0001756733; G0001756741; G0001756758; G0001756766; G0001756774; G0001756782; G0001756790; G0001756808; G0001756816; G0001756824; G0001756832; G0001756840; G0001756857; G0001756865; G0001756873; G0001756881; G0001756899; G0001756907; G0001756915; G0001756923; G0001756931; G0001756949; G0001756956; G0001756968; G0001756972; G0001756980; G0001757004; G0001757012; G0001757020; G0001757038; G0001757046; G0001757053; G0001757061; G0001757079; G0001757087; G0001757095; G0001757103; G0001757111; G0001757129; G0001757137; G0001757145; G0001757152; G0001757160; G0001757178; G0001757186; G0001757194; G0001757202; G0001757210; G0001757228; G0001757236; G0001757244; G0001757251; G0001757269; G0001757277; G0001757285; G0001757293; G0001757301; G0001757319; G0001757327; G0001757335; G0001757343; G0001757350; G0001757368; G0001757376; G0001757384; G0001757392; G0001757400; G0001757418; G0001757426; G0001757434; G0001757442; G0001757459; G0001757467; G0001757475; G0001757483; G0001757491; G0001757509; G0001757517; G0001757525; G0001757533; G0001757541; G0001757558; G0001757566; G0001757574; G0001757582; G0001757590; G0001757608; G0001757616; G0001757624; G0001757632; G0001757640; G0001757657; G0001757665; G0001757673; G0001757681; G0001757699; G0001757707; G0001757715; G0001757723; G0001757731; G0001757749; G0001757756; G0001757764; G0001757772; G0001757780; G0001757798; G0001757806; G0001757814; G0001757822; G0001757830; G0001757848; G0001757855; G0001757863; G0001757871; G0001757889; G0001757897; G0001757905; G0001757913; G0001757921; G0001757939; G0001757947; G0001757954; G0001757962; G0001757970; G0001757988; G0001757996; G0001758002; G0001758010; G0001758028; G0001758036; G0001758044; G0001758051; G0001758069; G0001758077; G0001758085; G0001758093; G0001758101; G0001758119; G0001758127; G0001758135; G0001758143; G0001758150; G0001758168; G0001758176; G0001758184; G0001758192; G0001758200; G0001758218; G0001758226; G0001758234; G0001758242; G0001758259; G0001758267; G0001758275; G0001758283; G0001758291; G0001758309; G0001758317; G0001758325; G0001758333; G0001758341; G0001758358; G0001758366; G0001758374; G0001758382; G0001758390; G0001758408; G0001758416; G0001758424; G0001758432; G0001758440; G0001758457; G0001758465; G0001758473; G0001758481; G0001758499; G0001758507; G0001758515; G0001758523; G0001758531; G0001758549; G0001758556; G0001758564; G0001758572; G0001758580; G0001758598; G0001758606; G0001758614; G0001758622; G0001758648; G0001758655; G0001758663; G0001758671; G0001758689; G0001758697; G0001758705; G0001758713; G0001758721; G0001758739; G0001758747; G0001758754; G0001758762; G0001758770; G0001758788; G0001758796; G0001758804; G0001758812; G0001758820; G0001758838; G0001758846; G0001758853; G0001758861; G0001758879; G0001758887; G0001758895; G0001758903; G0001758911; G0001758929; G0001758937; G0001758945; G0001758952; G0001758960; G0001758978; G0001758986; G0001758994; G0001759000; G0001759018; G0001759026; G0001759034; G0001759042; G0001759059; G0001759067; G0001759075; G0001759083; G0001759091; G0001759109; G0001759117; G0001759125; G0001759133; G0001759141; G0001759158; G0001759166; G0001759174; G0001759182; G0001759190; G0001759208; G0001759216; G0001759224; G0001759232; G0001759240; G0001759257; G0001759265; G0001759273; G0001759281; G0001759299; G0001759307; G0001759315; G0001759323; G0001759331; G0001759349; G0001759356; G0001759372; G0001759380; G0001759398; G0001759406; G0001759414; G0001759422; G0001759430; G0001759448; G0001759455; G0001759463; G0001759471; G0001759489; G0001759497; G0001759505; G0001759513; G0001759521; G0001759539; G0001759547; G0001759554; G0001759562; G0001759570; G0001759588; G0001759596; G0001759604; G0001759612; G0001759620; G0001759638; G0001759646; G0001759653; G0001759661; G0001759679; G0001759687; G0001759695; G0001759703; G0001759711; G0001759729; G0001759737; G0001759745; G0001759752; G0001759760; G0001759778; G0001759786; G0001759794; G0001759802; G0001759810; G0001759828; G0001759836; G0001759844; G0001759851; G0001759869; G0001759877; G0001759885; G0001759893; G0001759901; G0001759919; G0001759927; G0001759935; G0001759943; G0001759950; G0001759968; G0001759976; G0001759984; G0001759992; G0001760008; G0001760016; G0001760024; G0001760032; G0001760040; G0001760057; G0001760065; G0001760073; G0001760081; G0001760099; G0001760107; G0001760115; G0001760131; G0001760149; G0001760156; G0001760164; G0001760172; G0001760180; G0001760198; G0001760206; G0001760214; G0001760222; G0001760230; G0001760248; G0001760255; G0001760263; G0001760271; G0001760289; G0001760297; G0001760305; G0001760313; G0001760321; G0001760339; G0001760347; G0001760354; G0001760362; G0001760370; G0001760388; G0001760396; G0001760404; G0001760412; G0001760420; G0001760438; G0001760446; G0001760453; G0001760461; G0001760479; G0001760487; G0001760495; G0001760503; G0001760511; G0001760529; G0001760537; G0001760545; G0001760552; G0001760560; G0001760578; G0001760586; G0001760594; G0001760602; G0001760610; G0001760628; G0001760636; G0001760644; G0001760651; G0001760669; G0001760677; G0001760685; G0001760693; G0001760701; G0001760719; G0001760727; G0001760735; G0001760743; G0001760750; G0001760768; G0001760776; G0001760784; G0001760792; G0001760800; G0001760818; G0001760826; G0001760834; G0001760842; G0001760859; G0001760867; G0001760875; G0001760883; G0001760891; G0001760909; G0001760917; G0001760925; G0001760933; G0001760941; G0001760958; G0001760966; G0001760974; G0001760982; G0001760990; G0001761006; G0001761014; G0001761022; G0001761030; G0001761048; G0001761055; G0001761063; G0001761071; G0001761089; G0001761097; G0001761105; G0001761113; G0001761121; G0001761139; G0001761147; G0001761154; G0001761162; G0001761170; G0001761188; G0001761196; G0001761204; G0001761212; G0001761220; G0001761238; G0001761246; G0001761253; G0001761261; G0001761279; G0001761287; G0001761295; G0001761303; G0001761311; G0001761329; G0001761337; G0001761345; G0001761352; G0001761360; G0001761378; G0001761386; G0001761394; G0001761402; G0001761410; G0001761428; G0001761436; G0001761444; G0001761451; G0001761469; G0001761477; G0001761485; G0001761493; G0001761501; G0001761519; G0001761527; G0001761535; G0001761543; G0001761550; G0001761568; G0001761576; G0001761584; G0001761592; G0001761600; G0001761618; G0001761626; G0001761634; G0001761642; G0001761659; G0001761667; G0001761675; G0001761683; G0001761691; G0001761709; G0001761717; G0001761725; G0001761733; G0001761741; G0001761758; G0001761766; G0001761774; G0001761782; G0001761790; G0001761808; G0001761816; G0001761824; G0001761832; G0001761840; G0001761857; G0001761865; G0001761873; G0001761881; G0001761899; G0001761907; G0001761915; G0001761923; G0001761931; G0001761949; G0001761956; G0001761964; G0001761972; G0001761980; G0001761998; G0001762004; G0001762012; G0001762020; G0001762038; G0001762046; G0001762053; G0001762061; G0001762079; G0001762087; G0001762095; G0001762103; G0001762111; G0001762129; G0001762137; G0001762145; G0001762152; G0001762160; G0001762178; G0001762186; G0001762194; G0001762202; G0001762210; G0001762228; G0001762236; G0001762244; G0001762251; G0001762269; G0001762277; G0001762285; G0001762293; G0001762301; G0001762319; G0001762327; G0001762335; G0001762343; G0001762350; G0001762368; G0001762376; G0001762384; G0001762392; G0001762400; G0001762418; G0001762426; G0001762442; G0001762459; G0001762467; G0001762475; G0001762483; G0001762491; G0001762509; G0001762517; G0001762525; G0001762533; G0001762541; G0001762558; G0001762566; G0001762574; G0001762582; G0001762590; G0001762608; G0001762616; G0001762624; G0001762632; G0001762640; G0001762657; G0001762665; G0001762673; G0001762681; G0001762699; G0001762707; G0001762715; G0001762723; G0001762731; G0001762749; G0001762756; G0001762764; G0001762772; G0001762780; G0001762798; G0001762806; G0001762814; G0001762822; G0001762830; G0001762848; G0001762855; G0001762863; G0001762871; G0001762889; G0001762897; G0001762905; G0001762913; G0001762921; G0001762939; G0001762947; G0001762954; G0001762962; G0001762970; G0001762988; G0001762996; G0001763002; G0001763010; G0001763028; G0001763036; G0001763044; G0001763051; G0001763069; G0001763077; G0001763085; G0001763093; G0001763101; G0001763119; G0001763127; G0001763135; G0001763143; G0001763150; G0001763168; G0001763176; G0001763184; G0001763192; G0001763200</t>
+          <t>G000175480W; G0001745991; G0001746007; G0001746015; G0001746023; G0001746031; G0001746049; G0001746056; G0001746064; G0001746072; G0001746080; G0001746098; G0001746106; G0001746114; G0001746122; G0001746130; G0001746148; G0001746155; G0001746163; G0001746171; G0001746189; G0001746197; G0001746205; G0001746213; G0001746221; G0001746239; G0001746247; G0001746254; G0001746262; G0001746270; G0001746288; G0001746296; G0001746304; G0001746312; G0001746320; G0001746338; G0001746346; G0001746353; G0001746361; G0001746379; G0001746387; G0001746395; G0001746403; G0001746411; G0001746429; G0001746437; G0001746445; G0001746452; G0001746460; G0001746478; G0001746486; G0001746494; G0001746502; G0001746510; G0001746528; G0001746536; G0001746544; G0001746551; G0001746569; G0001746577; G0001746585; G0001746593; G0001746601; G0001746619; G0001746627; G0001746635; G0001746643; G0001746650; G0001746668; G0001746676; G0001746684; G0001746692; G0001746700; G0001746718; G0001746726; G0001746734; G0001746742; G0001746759; G0001746767; G0001746775; G0001746783; G0001746791; G0001746809; G0001746817; G0001746825; G0001746833; G0001746841; G0001746858; G0001746866; G0001746874; G0001746882; G0001746890; G0001746908; G0001746916; G0001746924; G0001746932; G0001746940; G0001746957; G0001746965; G0001746973; G0001746981; G0001746999; G0001747005; G0001747013; G0001747021; G0001747039; G0001747047; G0001747054; G0001747062; G0001747070; G0001747088; G0001747096; G0001747104; G0001747112; G0001747120; G0001747138; G0001747146; G0001747153; G0001747161; G0001747179; G0001747187; G0001747195; G0001747203; G0001747211; G0001747229; G0001747237; G0001747245; G0001747252; G0001747260; G0001747278; G0001747286; G0001747294; G0001747302; G0001747310; G0001747328; G0001747336; G0001747344; G0001747351; G0001747369; G0001747377; G0001747385; G0001747393; G0001747401; G0001747419; G0001747427; G0001747435; G0001747443; G0001747450; G0001747468; G0001747476; G0001747484; G0001747492; G0001747500; G0001747518; G0001747526; G0001747534; G0001747542; G0001747559; G0001747567; G0001747575; G0001747583; G0001747591; G0001747609; G0001747617; G0001747625; G0001747633; G0001747641; G0001747658; G0001747666; G0001747674; G0001747682; G0001747690; G0001747708; G0001747716; G0001747724; G0001747732; G0001747740; G0001747757; G0001747765; G0001747773; G0001747781; G0001747799; G0001747807; G0001747815; G0001747823; G0001747831; G0001747849; G0001747856; G0001747864; G0001747872; G0001747880; G0001747898; G0001747906; G0001747914; G0001747922; G0001747930; G0001747948; G0001747955; G0001747963; G0001747971; G0001747989; G0001747997; G0001748003; G0001748011; G0001748029; G0001748037; G0001748045; G0001748052; G0001748060; G0001748078; G0001748086; G0001748094; G0001748102; G0001748110; G0001748128; G0001748136; G0001748144; G0001748151; G0001748169; G0001748177; G0001748185; G0001748193; G0001748201; G0001748219; G0001748227; G0001748235; G0001748243; G0001748250; G0001748268; G0001748276; G0001748284; G0001748292; G0001748300; G0001748318; G0001748326; G0001748334; G0001748342; G0001748359; G0001748367; G0001748375; G0001748391; G0001748409; G0001748417; G0001748425; G0001748433; G0001748441; G0001748458; G0001748466; G0001748474; G0001748482; G0001748490; G0001748508; G0001748516; G0001748524; G0001748532; G0001748540; G0001748557; G0001748565; G0001748573; G0001748581; G0001748599; G0001748607; G0001748615; G0001748623; G0001748631; G0001748649; G0001748656; G0001748664; G0001748672; G0001748680; G0001748698; G0001748706; G0001748714; G0001748722; G0001748730; G0001748748; G0001748755; G0001748763; G0001748771; G0001748789; G0001748797; G0001748805; G0001748813; G0001748821; G0001748839; G0001748847; G0001748854; G0001748862; G0001748870; G0001748888; G0001748896; G0001748904; G0001748912; G0001748920; G0001748938; G0001748946; G0001748953; G0001748961; G0001748979; G0001748987; G0001748995; G0001749001; G0001749019; G0001749027; G0001749035; G0001749043; G0001749050; G0001749068; G0001749076; G0001749084; G0001749092; G0001749100; G0001749118; G0001749126; G0001749134; G0001749142; G0001749159; G0001749167; G0001749175; G0001749183; G0001749191; G0001749209; G0001749217; G0001749225; G0001749233; G0001749241; G0001749258; G0001749266; G0001749274; G0001749282; G0001749290; G0001749308; G0001749316; G0001749324; G0001749332; G0001749340; G0001749357; G0001749365; G0001749373; G0001749381; G0001749399; G0001749407; G0001749415; G0001749423; G0001749431; G0001749449; G0001749456; G0001749464; G0001749472; G0001749480; G0001749498; G0001749506; G0001749514; G0001749522; G0001749530; G0001749548; G0001749555; G0001749563; G0001749571; G0001749589; G0001749597; G0001749605; G0001749613; G0001749621; G0001749639; G0001749647; G0001749654; G0001749662; G0001749670; G0001749688; G0001749696; G0001749704; G0001749712; G0001749720; G0001749738; G0001749746; G0001749753; G0001749761; G0001749779; G0001749787; G0001749795; G0001749803; G0001749811; G0001749829; G0001749837; G0001749845; G0001749852; G0001749860; G0001749878; G0001749886; G0001749894; G0001749902; G0001749910; G0001749928; G0001749936; G0001749944; G0001749951; G0001749969; G0001749977; G0001749985; G0001749993; G0001750009; G0001750017; G0001750025; G0001750033; G0001750041; G0001750058; G0001750066; G0001750074; G0001750082; G0001750090; G0001750108; G0001750116; G0001750124; G0001750132; G0001750140; G0001750157; G0001750165; G0001750173; G0001750181; G0001750199; G0001750207; G0001750215; G0001750223; G0001750231; G0001750249; G0001750256; G0001750264; G0001750272; G0001750280; G0001750298; G0001750306; G0001750314; G0001750322; G0001750330; G0001750348; G0001750355; G0001750363; G0001750371; G0001750389; G0001750397; G0001750405; G0001750413; G0001750421; G0001750439; G0001750447; G0001750454; G0001750462; G0001750470; G0001750488; G0001750496; G0001750512; G0001750538; G0001750546; G0001750553; G0001750561; G0001750579; G0001750587; G0001750595; G0001750603; G0001750611; G0001750629; G0001750637; G0001750645; G0001750652; G0001750660; G0001750678; G0001750686; G0001750694; G0001750702; G0001750710; G0001750728; G0001750736; G0001750744; G0001750751; G0001750769; G0001750777; G0001750785; G0001750793; G0001750801; G0001750819; G0001750827; G0001750835; G0001750843; G0001750850; G0001750868; G0001750876; G0001750884; G0001750892; G0001750900; G0001750918; G0001750926; G0001750934; G0001750942; G0001750959; G0001750967; G0001750975; G0001750983; G0001750991; G0001751007; G0001751015; G0001751023; G0001751031; G0001751049; G0001751056; G0001751064; G0001751072; G0001751080; G0001751098; G0001751106; G0001751114; G0001751122; G0001751130; G0001751148; G0001751155; G0001751163; G0001751171; G0001751189; G0001751197; G0001751205; G0001751213; G0001751221; G0001751239; G0001751247; G0001751254; G0001751262; G0001751270; G0001751288; G0001751296; G0001751304; G0001751312; G0001751320; G0001751338; G0001751346; G0001751353; G0001751361; G0001751379; G0001751387; G0001751395; G0001751403; G0001751411; G0001751429; G0001751437; G0001751445; G0001751452; G0001751460; G0001751478; G0001751486; G0001751494; G0001751502; G0001751510; G0001751528; G0001751536; G0001751544; G0001751551; G0001751569; G0001751577; G0001751585; G0001751593; G0001751601; G0001751619; G0001751627; G0001751635; G0001751643; G0001751650; G0001751668; G0001751676; G0001751684; G0001751692; G0001751700; G0001751718; G0001751726; G0001751734; G0001751742; G0001751759; G0001751767; G0001751775; G0001751783; G0001751791; G0001751809; G0001751817; G0001751825; G0001751833; G0001751841; G0001751858; G0001751866; G0001751874; G0001751882; G0001751890; G0001751908; G0001751916; G0001751924; G0001751932; G0001751940; G0001751957; G0001751965; G0001751973; G0001751981; G0001751999; G0001752005; G0001752013; G0001752021; G0001752039; G0001752047; G0001752054; G0001752062; G0001752070; G0001752088; G0001752096; G0001752104; G0001752112; G0001752120; G0001752138; G0001752146; G0001752153; G0001752161; G0001752179; G0001752187; G0001752195; G0001752203; G0001752211; G0001752229; G0001752237; G0001752245; G0001752252; G0001752260; G0001752278; G0001752286; G0001752294; G0001752302; G0001752310; G0001752328; G0001752336; G0001752344; G0001752351; G0001752369; G0001752377; G0001752385; G0001752393; G0001752401; G0001752419; G0001752427; G0001752435; G0001752443; G0001752450; G0001752468; G0001752476; G0001752484; G0001752492; G0001752500; G0001752518; G0001752526; G0001752534; G0001752542; G0001752559; G0001752567; G0001752575; G0001752583; G0001752591; G0001752609; G0001752617; G0001752625; G0001752633; G0001752641; G0001752658; G0001752666; G0001752674; G0001752682; G0001752690; G0001752708; G0001752716; G0001752724; G0001752732; G0001752740; G0001752757; G0001752765; G0001752773; G0001752781; G0001752799; G0001752807; G0001752815; G0001752823; G0001752831; G0001752849; G0001752856; G0001752864; G0001752872; G0001752880; G0001752898; G0001752906; G0001752914; G0001752922; G0001752930; G0001752948; G0001752955; G0001752963; G0001752964; G0001752971; G0001752989; G0001752997; G0001753003; G0001753011; G0001753029; G0001753037; G0001753045; G0001753052; G0001753060; G0001753078; G0001753086; G0001753094; G0001753102; G0001753110; G0001753128; G0001753136; G0001753144; G0001753151; G0001753169; G0001753177; G0001753185; G0001753193; G0001753201; G0001753219; G0001753227; G0001753235; G0001753243; G0001753250; G0001753268; G0001753276; G0001753284; G0001753292; G0001753300; G0001753318; G0001753326; G0001753334; G0001753342; G0001753359; G0001753367; G0001753375; G0001753383; G0001753391; G0001753409; G0001753417; G0001753425; G0001753433; G0001753441; G0001753458; G0001753466; G0001753474; G0001753482; G0001753490; G0001753508; G0001753516; G0001753524; G0001753532; G0001753540; G0001753557; G0001753565; G0001753573; G0001753581; G0001753599; G0001753607; G0001753615; G0001753623; G0001753631; G0001753649; G0001753656; G0001753664; G0001753672; G0001753680; G0001753698; G0001753706; G0001753714; G0001753722; G0001753730; G0001753748; G0001753755; G0001753763; G0001753771; G0001753789; G0001753797; G0001753805; G0001753813; G0001753821; G0001753839; G0001753847; G0001753854; G0001753862; G0001753870; G0001753888; G0001753896; G0001753904; G0001753912; G0001753920; G0001753938; G0001753946; G0001753953; G0001753961; G0001753979; G0001753987; G0001753995; G0001754001; G0001754019; G0001754027; G0001754035; G0001754043; G0001754050; G0001754068; G0001754076; G0001754084; G0001754092; G0001754100; G0001754118; G0001754126; G0001754142; G0001754159; G0001754167; G0001754175; G0001754183; G0001754191; G0001754209; G0001754217; G0001754225; G0001754233; G0001754241; G0001754258; G0001754266; G0001754274; G0001754282; G0001754290; G0001754308; G0001754316; G0001754324; G0001754332; G0001754340; G0001754357; G0001754365; G0001754373; G0001754381; G0001754399; G0001754407; G0001754415; G0001754423; G0001754431; G0001754449; G0001754456; G0001754464; G0001754472; G0001754480; G0001754498; G0001754506; G0001754514; G0001754522; G0001754530; G0001754548; G0001754555; G0001754563; G0001754571; G0001754589; G0001754597; G0001754605; G0001754613; G0001754621; G0001754639; G0001754647; G0001754654; G0001754662; G0001754670; G0001754688; G0001754696; G0001754704; G0001754712; G0001754720; G0001754738; G0001754746; G0001754753; G0001754761; G0001754779; G0001754787; G0001754795; G0001754811; G0001754829; G0001754837; G0001754845; G0001754852; G0001754860; G0001754878; G0001754886; G0001754894; G0001754902; G0001754910; G0001754928; G0001754936; G0001754944; G0001754951; G0001754969; G0001754977; G0001754985; G0001754993; G0001755008; G0001755016; G0001755024; G0001755032; G0001755040; G0001755057; G0001755065; G0001755073; G0001755081; G0001755099; G0001755107; G0001755115; G0001755123; G0001755131; G0001755149; G0001755156; G0001755164; G0001755172; G0001755180; G0001755198; G0001755206; G0001755214; G0001755222; G0001755230; G0001755248; G0001755255; G0001755263; G0001755271; G0001755289; G0001755297; G0001755305; G0001755313; G0001755321; G0001755339; G0001755347; G0001755354; G0001755362; G0001755370; G0001755388; G0001755396; G0001755404; G0001755412; G0001755420; G0001755438; G0001755446; G0001755453; G0001755461; G0001755479; G0001755487; G0001755495; G0001755503; G0001755511; G0001755529; G0001755537; G0001755545; G0001755552; G0001755560; G0001755578; G0001755586; G0001755594; G0001755602; G0001755610; G0001755628; G0001755636; G0001755644; G0001755651; G0001755669; G0001755677; G0001755685; G0001755693; G0001755701; G0001755719; G0001755727; G0001755735; G0001755743; G0001755750; G0001755768; G0001755776; G0001755784; G0001755792; G0001755800; G0001755818; G0001755826; G0001755834; G0001755842; G0001755859; G0001755867; G0001755875; G0001755883; G0001755891; G0001755900; G0001755909; G0001755917; G0001755925; G0001755933; G0001755941; G0001755958; G0001755966; G0001755974; G0001755982; G0001756006; G0001756014; G0001756022; G0001756030; G0001756048; G0001756055; G0001756063; G0001756071; G0001756089; G0001756097; G0001756105; G0001756113; G0001756121; G0001756139; G0001756147; G0001756154; G0001756162; G0001756170; G0001756188; G0001756196; G0001756204; G0001756212; G0001756220; G0001756238; G0001756246; G0001756253; G0001756261; G0001756279; G0001756287; G0001756295; G0001756303; G0001756311; G0001756329; G0001756337; G0001756345; G0001756352; G0001756360; G0001756378; G0001756386; G0001756394; G0001756402; G0001756410; G0001756428; G0001756436; G0001756444; G0001756451; G0001756469; G0001756477; G0001756485; G0001756493; G0001756501; G0001756519; G0001756527; G0001756535; G0001756543; G0001756550; G0001756568; G0001756576; G0001756584; G0001756592; G0001756600; G0001756618; G0001756626; G0001756634; G0001756642; G0001756659; G0001756667; G0001756675; G0001756683; G0001756691; G0001756709; G0001756717; G0001756725; G0001756733; G0001756741; G0001756758; G0001756766; G0001756774; G0001756782; G0001756790; G0001756808; G0001756816; G0001756824; G0001756832; G0001756840; G0001756857; G0001756865; G0001756873; G0001756881; G0001756899; G0001756907; G0001756915; G0001756923; G0001756931; G0001756949; G0001756956; G0001756968; G0001756972; G0001756980; G0001757004; G0001757012; G0001757020; G0001757038; G0001757046; G0001757053; G0001757061; G0001757079; G0001757087; G0001757095; G0001757103; G0001757111; G0001757129; G0001757137; G0001757145; G0001757152; G0001757160; G0001757178; G0001757186; G0001757194; G0001757202; G0001757210; G0001757228; G0001757236; G0001757244; G0001757251; G0001757269; G0001757277; G0001757285; G0001757293; G0001757301; G0001757319; G0001757327; G0001757335; G0001757343; G0001757350; G0001757368; G0001757376; G0001757384; G0001757392; G0001757400; G0001757418; G0001757426; G0001757434; G0001757442; G0001757459; G0001757467; G0001757475; G0001757483; G0001757491; G0001757509; G0001757517; G0001757525; G0001757533; G0001757541; G0001757558; G0001757566; G0001757574; G0001757582; G0001757590; G0001757608; G0001757616; G0001757624; G0001757632; G0001757640; G0001757657; G0001757665; G0001757673; G0001757681; G0001757699; G0001757707; G0001757715; G0001757723; G0001757731; G0001757749; G0001757756; G0001757764; G0001757772; G0001757780; G0001757798; G0001757806; G0001757814; G0001757822; G0001757830; G0001757848; G0001757855; G0001757863; G0001757871; G0001757889; G0001757897; G0001757905; G0001757913; G0001757921; G0001757939; G0001757947; G0001757954; G0001757962; G0001757970; G0001757988; G0001757996; G0001758002; G0001758010; G0001758028; G0001758036; G0001758044; G0001758051; G0001758069; G0001758077; G0001758085; G0001758093; G0001758101; G0001758119; G0001758127; G0001758135; G0001758143; G0001758150; G0001758168; G0001758176; G0001758184; G0001758192; G0001758200; G0001758218; G0001758226; G0001758234; G0001758242; G0001758259; G0001758267; G0001758275; G0001758283; G0001758291; G0001758309; G0001758317; G0001758325; G0001758333; G0001758341; G0001758358; G0001758366; G0001758374; G0001758382; G0001758390; G0001758408; G0001758416; G0001758424; G0001758432; G0001758440; G0001758457; G0001758465; G0001758473; G0001758481; G0001758499; G0001758507; G0001758515; G0001758523; G0001758531; G0001758549; G0001758556; G0001758564; G0001758572; G0001758580; G0001758598; G0001758606; G0001758614; G0001758622; G0001758648; G0001758655; G0001758663; G0001758671; G0001758689; G0001758697; G0001758705; G0001758713; G0001758721; G0001758739; G0001758747; G0001758754; G0001758762; G0001758770; G0001758788; G0001758796; G0001758804; G0001758812; G0001758820; G0001758838; G0001758846; G0001758853; G0001758861; G0001758879; G0001758887; G0001758895; G0001758903; G0001758911; G0001758929; G0001758937; G0001758945; G0001758952; G0001758960; G0001758978; G0001758986; G0001758994; G0001759000; G0001759018; G0001759026; G0001759034; G0001759042; G0001759059; G0001759067; G0001759075; G0001759083; G0001759091; G0001759109; G0001759117; G0001759125; G0001759133; G0001759141; G0001759158; G0001759166; G0001759174; G0001759182; G0001759190; G0001759208; G0001759216; G0001759224; G0001759232; G0001759240; G0001759257; G0001759265; G0001759273; G0001759281; G0001759299; G0001759307; G0001759315; G0001759323; G0001759331; G0001759349; G0001759356; G0001759372; G0001759380; G0001759398; G0001759406; G0001759414; G0001759422; G0001759430; G0001759448; G0001759455; G0001759463; G0001759471; G0001759489; G0001759497; G0001759505; G0001759513; G0001759521; G0001759539; G0001759547; G0001759554; G0001759562; G0001759570; G0001759588; G0001759596; G0001759604; G0001759612; G0001759620; G0001759638; G0001759646; G0001759653; G0001759661; G0001759679; G0001759687; G0001759695; G0001759703; G0001759711; G0001759729; G0001759737; G0001759745; G0001759752; G0001759760; G0001759778; G0001759786; G0001759794; G0001759802; G0001759810; G0001759828; G0001759836; G0001759844; G0001759851; G0001759869; G0001759877; G0001759885; G0001759893; G0001759901; G0001759919; G0001759927; G0001759935; G0001759943; G0001759950; G0001759968; G0001759976; G0001759984; G0001759992; G0001760008; G0001760016; G0001760024; G0001760032; G0001760040; G0001760057; G0001760065; G0001760073; G0001760081; G0001760099; G0001760107; G0001760115; G0001760131; G0001760149; G0001760156; G0001760164; G0001760172; G0001760180; G0001760198; G0001760206; G0001760214; G0001760222; G0001760230; G0001760248; G0001760255; G0001760263; G0001760271; G0001760289; G0001760297; G0001760305; G0001760313; G0001760321; G0001760339; G0001760347; G0001760354; G0001760362; G0001760370; G0001760388; G0001760396; G0001760404; G0001760412; G0001760420; G0001760438; G0001760446; G0001760453; G0001760461; G0001760479; G0001760487; G0001760495; G0001760503; G0001760511; G0001760529; G0001760537; G0001760545; G0001760552; G0001760560; G0001760578; G0001760586; G0001760594; G0001760602; G0001760610; G0001760628; G0001760636; G0001760644; G0001760651; G0001760669; G0001760677; G0001760685; G0001760693; G0001760701; G0001760719; G0001760727; G0001760735; G0001760743; G0001760750; G0001760768; G0001760776; G0001760784; G0001760792; G0001760800; G0001760818; G0001760826; G0001760834; G0001760842; G0001760859; G0001760867; G0001760875; G0001760883; G0001760891; G0001760909; G0001760917; G0001760925; G0001760933; G0001760941; G0001760958; G0001760966; G0001760974; G0001760982; G0001760990; G0001761006; G0001761014; G0001761022; G0001761030; G0001761048; G0001761055; G0001761063; G0001761071; G0001761089; G0001761097; G0001761105; G0001761113; G0001761121; G0001761139; G0001761147; G0001761154; G0001761162; G0001761170; G0001761188; G0001761196; G0001761204; G0001761212; G0001761220; G0001761238; G0001761246; G0001761253; G0001761261; G0001761279; G0001761287; G0001761295; G0001761303; G0001761311; G0001761329; G0001761337; G0001761345; G0001761352; G0001761360; G0001761378; G0001761386; G0001761394; G0001761402; G0001761410; G0001761428; G0001761436; G0001761444; G0001761451; G0001761469; G0001761477; G0001761485; G0001761493; G0001761501; G0001761519; G0001761527; G0001761535; G0001761543; G0001761550; G0001761568; G0001761576; G0001761584; G0001761592; G0001761600; G0001761618; G0001761626; G0001761634; G0001761642; G0001761659; G0001761667; G0001761675; G0001761683; G0001761691; G0001761709; G0001761717; G0001761725; G0001761733; G0001761741; G0001761758; G0001761766; G0001761774; G0001761782; G0001761790; G0001761808; G0001761816; G0001761824; G0001761832; G0001761840; G0001761857; G0001761865; G0001761873; G0001761881; G0001761899; G0001761907; G0001761915; G0001761923; G0001761931; G0001761949; G0001761956; G0001761964; G0001761972; G0001761980; G0001761998; G0001762004; G0001762012; G0001762020; G0001762038; G0001762046; G0001762053; G0001762061; G0001762079; G0001762087; G0001762095; G0001762103; G0001762111; G0001762129; G0001762137; G0001762145; G0001762152; G0001762160; G0001762178; G0001762186; G0001762194; G0001762202; G0001762210; G0001762228; G0001762236; G0001762244; G0001762251; G0001762269; G0001762277; G0001762285; G0001762293; G0001762301; G0001762319; G0001762327; G0001762335; G0001762343; G0001762350; G0001762368; G0001762376; G0001762384; G0001762392; G0001762400; G0001762418; G0001762426; G0001762442; G0001762459; G0001762467; G0001762475; G0001762483; G0001762491; G0001762509; G0001762517; G0001762525; G0001762533; G0001762541; G0001762558; G0001762566; G0001762574; G0001762582; G0001762590; G0001762608; G0001762616; G0001762624; G0001762632; G0001762640; G0001762657; G0001762665; G0001762673; G0001762681; G0001762699; G0001762707; G0001762715; G0001762723; G0001762731; G0001762749; G0001762756; G0001762764; G0001762772; G0001762780; G0001762798; G0001762806; G0001762814; G0001762822; G0001762830; G0001762848; G0001762855; G0001762863; G0001762871; G0001762889; G0001762897; G0001762905; G0001762913; G0001762921; G0001762939; G0001762947; G0001762954; G0001762962; G0001762970; G0001762988; G0001762996; G0001763002; G0001763010; G0001763028; G0001763036; G0001763044; G0001763051; G0001763069; G0001763077; G0001763085; G0001763093; G0001763101; G0001763119; G0001763127; G0001763135; G0001763143; G0001763150; G0001763168; G0001763176; G0001763184; G0001763192; G0001763200; G00017505043</t>
         </is>
       </c>
     </row>
